--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\santo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E2B74E5-E6F3-4432-9764-F1C1BA8B1430}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C689CF22-E1FA-4E34-BB2E-F901723F1FF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="12">
   <si>
     <t>Date</t>
   </si>
@@ -50,13 +50,19 @@
   </si>
   <si>
     <t>Sneha and Bhoomika</t>
+  </si>
+  <si>
+    <t>Printer</t>
+  </si>
+  <si>
+    <t>Santosh</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -71,8 +77,15 @@
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
+      <sz val="14"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="5">
@@ -108,16 +121,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFCCCCCC"/>
+        <color indexed="64"/>
       </left>
       <right style="thin">
-        <color rgb="FFCCCCCC"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color rgb="FFCCCCCC"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFCCCCCC"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -125,16 +138,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -438,12 +454,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="35" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="3" max="3" width="35.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -479,15 +495,26 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" ht="18" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="4" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\santo\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\1A1\Playisto\Claude work\Tools\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C689CF22-E1FA-4E34-BB2E-F901723F1FF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ABDE372-29E1-42CC-9202-6233953D237B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="13">
   <si>
     <t>Date</t>
   </si>
@@ -56,6 +56,9 @@
   </si>
   <si>
     <t>Santosh</t>
+  </si>
+  <si>
+    <t>Mini JCB</t>
   </si>
 </sst>
 </file>
@@ -138,7 +141,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -151,6 +154,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -454,7 +460,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -517,6 +523,17 @@
         <v>11</v>
       </c>
     </row>
+    <row r="6" spans="1:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
+        <v>46194</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\1A1\Playisto\Claude work\Tools\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ABDE372-29E1-42CC-9202-6233953D237B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07F0156C-87E0-4652-AFB7-0A4AEF14D85F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="13">
   <si>
     <t>Date</t>
   </si>
@@ -155,7 +155,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -524,8 +524,8 @@
       </c>
     </row>
     <row r="6" spans="1:3" ht="18" x14ac:dyDescent="0.3">
-      <c r="A6" s="5">
-        <v>46194</v>
+      <c r="A6" s="5" t="s">
+        <v>3</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>12</v>

--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\1A1\Playisto\Claude work\Tools\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07F0156C-87E0-4652-AFB7-0A4AEF14D85F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C38CF919-FBBE-4256-8148-67D95425AECF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
   <si>
     <t>Date</t>
   </si>
@@ -59,6 +59,9 @@
   </si>
   <si>
     <t>Mini JCB</t>
+  </si>
+  <si>
+    <t>21-06-2026</t>
   </si>
 </sst>
 </file>
@@ -525,7 +528,7 @@
     </row>
     <row r="6" spans="1:3" ht="18" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>12</v>

--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\1A1\Playisto\Claude work\Tools\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C38CF919-FBBE-4256-8148-67D95425AECF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECFD8AB4-4567-4CF2-915A-E5571D5ADE31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="12">
   <si>
     <t>Date</t>
   </si>
@@ -46,22 +46,16 @@
     <t>HESCOM office</t>
   </si>
   <si>
-    <t>Sadanand Camera work</t>
-  </si>
-  <si>
     <t>Sneha and Bhoomika</t>
   </si>
   <si>
-    <t>Printer</t>
-  </si>
-  <si>
-    <t>Santosh</t>
-  </si>
-  <si>
     <t>Mini JCB</t>
   </si>
   <si>
     <t>21-06-2026</t>
+  </si>
+  <si>
+    <t>6 months Unpaid Partial</t>
   </si>
 </sst>
 </file>
@@ -463,7 +457,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -504,37 +498,26 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="18" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>3</v>
+    <row r="4" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>10</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>8</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="18" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="18" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\1A1\Playisto\Claude work\Tools\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECFD8AB4-4567-4CF2-915A-E5571D5ADE31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB7BC508-6D38-4C9F-B210-37B2312ECECB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="15">
   <si>
     <t>Date</t>
   </si>
@@ -31,31 +31,40 @@
     <t>Assigned To</t>
   </si>
   <si>
-    <t>20-06-2026</t>
-  </si>
-  <si>
-    <t>Siddhant 5:30 am to 7 am fee</t>
-  </si>
-  <si>
-    <t>Bhoomika and Swati</t>
-  </si>
-  <si>
     <t>Satish</t>
   </si>
   <si>
-    <t>HESCOM office</t>
-  </si>
-  <si>
     <t>Sneha and Bhoomika</t>
   </si>
   <si>
-    <t>Mini JCB</t>
-  </si>
-  <si>
-    <t>21-06-2026</t>
-  </si>
-  <si>
     <t>6 months Unpaid Partial</t>
+  </si>
+  <si>
+    <t>JCB - 11th or 12th July</t>
+  </si>
+  <si>
+    <t>8-07-2026</t>
+  </si>
+  <si>
+    <t>Splendour rim repair - URGENT</t>
+  </si>
+  <si>
+    <t>Unpaid Partial June - Critical</t>
+  </si>
+  <si>
+    <t>Swati Bhoomika</t>
+  </si>
+  <si>
+    <t>12-07-2026</t>
+  </si>
+  <si>
+    <t>Sales invoice printouts</t>
+  </si>
+  <si>
+    <t>Purchase invoice in Vyapar</t>
+  </si>
+  <si>
+    <t>Sneha</t>
   </si>
 </sst>
 </file>
@@ -457,7 +466,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -477,47 +486,69 @@
       </c>
     </row>
     <row r="2" spans="1:3" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>3</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>8</v>
+      <c r="B6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\1A1\Playisto\Claude work\Tools\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB7BC508-6D38-4C9F-B210-37B2312ECECB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8FEB877-8901-4E27-BC1B-7EE1C91CD232}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -84,6 +84,7 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="14"/>
@@ -161,7 +162,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
